--- a/EXCEL/Formula Excel Template.xlsx
+++ b/EXCEL/Formula Excel Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camda\Downloads\CODING\Learning Data Science\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camda\OneDrive\Documents\GitHub\Learning_Data_Analytics-Science\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C8D36C-6DAA-42E8-9256-BC0901FE3015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C6995D-CBBB-4868-9FEC-B2D8FD47FCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="10" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="LeftRight" sheetId="4" r:id="rId4"/>
     <sheet name="DateToText" sheetId="3" r:id="rId5"/>
     <sheet name="TRIM" sheetId="6" r:id="rId6"/>
-    <sheet name="Substitute" sheetId="7" r:id="rId7"/>
-    <sheet name="SUM-SumIF" sheetId="12" r:id="rId8"/>
-    <sheet name="Count-CountIF" sheetId="5" r:id="rId9"/>
-    <sheet name="Concatenate" sheetId="1" r:id="rId10"/>
+    <sheet name="Concatenate" sheetId="1" r:id="rId7"/>
+    <sheet name="Substitute" sheetId="7" r:id="rId8"/>
+    <sheet name="SUM-SumIF" sheetId="12" r:id="rId9"/>
+    <sheet name="Count-CountIF" sheetId="5" r:id="rId10"/>
     <sheet name="Days-NetworkDays" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="96">
   <si>
     <t>FirstName</t>
   </si>
@@ -286,9 +308,6 @@
     <t>COUNTIFS</t>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>Min</t>
   </si>
   <si>
@@ -308,6 +327,33 @@
   </si>
   <si>
     <t>Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max </t>
+  </si>
+  <si>
+    <t>LEFT</t>
+  </si>
+  <si>
+    <t>RIGHT</t>
+  </si>
+  <si>
+    <t>SalesMan</t>
+  </si>
+  <si>
+    <t>Regional manager</t>
+  </si>
+  <si>
+    <t>Supplier relations</t>
+  </si>
+  <si>
+    <t>TRIM(PROPER())</t>
+  </si>
+  <si>
+    <t>5-6/2001</t>
   </si>
 </sst>
 </file>
@@ -349,10 +395,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,7 +717,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -706,10 +753,10 @@
         <v>37</v>
       </c>
       <c r="J1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" t="s">
         <v>80</v>
-      </c>
-      <c r="K1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -740,8 +787,14 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1">
+        <f>MAX(H2:H10)</f>
+        <v>37933</v>
+      </c>
+      <c r="K2" s="1">
+        <f>MIN(H2:H10)</f>
+        <v>35040</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -771,6 +824,14 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3">
+        <f>MAX(G2:G10)</f>
+        <v>65000</v>
+      </c>
+      <c r="K3">
+        <f>MIN(G2:G10)</f>
+        <v>36000</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -973,6 +1034,11 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -981,22 +1047,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB977C31-5FD1-4473-A6A1-29ABAD3F7755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D217F6E-9452-40AF-AFA2-377600A25F44}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1025,10 +1087,16 @@
         <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="K1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1056,8 +1124,20 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <f>COUNT(G2:G10)</f>
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(G2:G10,"&gt;40000")</f>
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIFS(G2:G10,"&gt;40000",E2:E10,"Male",F2:F10,"Salesman")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1086,7 +1166,7 @@
         <v>42287</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1115,7 +1195,7 @@
         <v>42986</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1144,7 +1224,7 @@
         <v>42341</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1173,7 +1253,7 @@
         <v>42977</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -1202,7 +1282,7 @@
         <v>41528</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -1231,7 +1311,7 @@
         <v>41551</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -1260,7 +1340,7 @@
         <v>42116</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1287,18 +1367,6 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H11" t="str">
-        <f t="shared" ref="H11:H12" si="0">CONCATENATE(B11," ",C11)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H12" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
@@ -1316,6 +1384,7 @@
   <cols>
     <col min="8" max="8" width="14.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1347,10 +1416,10 @@
         <v>37</v>
       </c>
       <c r="J1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" t="s">
         <v>84</v>
-      </c>
-      <c r="K1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1381,6 +1450,14 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2:J10">_xlfn.DAYS(I2:I10,H2:H10)</f>
+        <v>5056</v>
+      </c>
+      <c r="K2">
+        <f>NETWORKDAYS(H2,I2)</f>
+        <v>3611</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1410,6 +1487,13 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J3">
+        <v>5851</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K10" si="0">NETWORKDAYS(H3,I3)</f>
+        <v>4180</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -1439,6 +1523,13 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="J4">
+        <v>6275</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>4484</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1468,6 +1559,13 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J5">
+        <v>5811</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>4152</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1497,6 +1595,13 @@
       <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="J6">
+        <v>5960</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>4258</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1526,6 +1631,13 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J7">
+        <v>4511</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>3223</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1555,6 +1667,13 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J8">
+        <v>3595</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>2568</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1584,6 +1703,13 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J9">
+        <v>4700</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>3358</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1612,6 +1738,13 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J10">
+        <v>4273</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>3053</v>
       </c>
     </row>
   </sheetData>
@@ -1661,10 +1794,10 @@
         <v>37</v>
       </c>
       <c r="J1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" t="s">
         <v>82</v>
-      </c>
-      <c r="K1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1695,6 +1828,14 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">IF(D2:D10 &gt;= 30,"Old","Young")</f>
+        <v>Old</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">_xlfn.IFS(F2:F10 = "Salesman", "Sales", F2:F10 = "HR", "Fire", F2:F10 = "Regional Manager", "Give Christmas Bonus")</f>
+        <v>Sales</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1724,6 +1865,12 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K3" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -1753,6 +1900,12 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>Young</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Sales</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1782,6 +1935,12 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K5" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1811,6 +1970,12 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Fire</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1840,6 +2005,12 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Give Christmas Bonus</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1869,6 +2040,12 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K8" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1898,6 +2075,12 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Sales</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1926,6 +2109,12 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Old</v>
+      </c>
+      <c r="K10" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -2007,6 +2196,10 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2:J10">LEN(E2:E10)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -2036,6 +2229,9 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -2065,6 +2261,9 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -2094,6 +2293,9 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -2123,6 +2325,9 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -2152,6 +2357,9 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -2181,6 +2389,9 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -2210,6 +2421,9 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -2238,6 +2452,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2250,14 +2467,24 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2289,16 +2516,19 @@
         <v>38</v>
       </c>
       <c r="K1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" t="s">
         <v>86</v>
       </c>
-      <c r="L1" t="s">
-        <v>87</v>
-      </c>
       <c r="M1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="N1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2329,8 +2559,24 @@
       <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">LEFT(F2:F10,5)</f>
+        <v>Sales</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">RIGHT(F2:F10,3)</f>
+        <v>man</v>
+      </c>
+      <c r="M2" t="str" cm="1">
+        <f t="array" ref="M2:M10">LEFT(G2:G10,2)</f>
+        <v>45</v>
+      </c>
+      <c r="N2" t="str" cm="1">
+        <f t="array" ref="N2:N10">RIGHT(I2:I10,4)</f>
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -2361,8 +2607,20 @@
       <c r="J3" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K3" t="str">
+        <v>Recep</v>
+      </c>
+      <c r="L3" t="str">
+        <v>ist</v>
+      </c>
+      <c r="M3" t="str">
+        <v>36</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -2393,8 +2651,20 @@
       <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K4" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="L4" t="str">
+        <v>man</v>
+      </c>
+      <c r="M4" t="str">
+        <v>63</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -2425,8 +2695,20 @@
       <c r="J5" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K5" t="str">
+        <v>Accou</v>
+      </c>
+      <c r="L5" t="str">
+        <v>ant</v>
+      </c>
+      <c r="M5" t="str">
+        <v>47</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -2457,8 +2739,20 @@
       <c r="J6" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K6" t="str">
+        <v>HR</v>
+      </c>
+      <c r="L6" t="str">
+        <v>HR</v>
+      </c>
+      <c r="M6" t="str">
+        <v>50</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -2489,8 +2783,20 @@
       <c r="J7" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K7" t="str">
+        <v>Regio</v>
+      </c>
+      <c r="L7" t="str">
+        <v>ger</v>
+      </c>
+      <c r="M7" t="str">
+        <v>65</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -2521,8 +2827,20 @@
       <c r="J8" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K8" t="str">
+        <v>Suppl</v>
+      </c>
+      <c r="L8" t="str">
+        <v>ons</v>
+      </c>
+      <c r="M8" t="str">
+        <v>41</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -2553,8 +2871,20 @@
       <c r="J9" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K9" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="L9" t="str">
+        <v>man</v>
+      </c>
+      <c r="M9" t="str">
+        <v>48</v>
+      </c>
+      <c r="N9" t="str">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -2584,6 +2914,18 @@
       </c>
       <c r="J10" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Accou</v>
+      </c>
+      <c r="L10" t="str">
+        <v>ant</v>
+      </c>
+      <c r="M10" t="str">
+        <v>42</v>
+      </c>
+      <c r="N10" t="str">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>
@@ -2596,14 +2938,22 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2635,7 +2985,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2654,7 +3004,7 @@
       <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>45000</v>
       </c>
       <c r="H2" s="1">
@@ -2663,9 +3013,17 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TEXT(H2:H10,"dd/mm/yyyy")</f>
+        <v>02/11/2001</v>
+      </c>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">TEXT(J3:J11,"dd/mm/yyyy")</f>
+        <v>10/03/1999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -2684,7 +3042,7 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>36000</v>
       </c>
       <c r="H3" s="1">
@@ -2693,9 +3051,15 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>03/10/1999</v>
+      </c>
       <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="str">
+        <v>07/04/2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -2714,7 +3078,7 @@
       <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>63000</v>
       </c>
       <c r="H4" s="1">
@@ -2723,9 +3087,15 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>04/07/2000</v>
+      </c>
       <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="str">
+        <v>01/05/2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -2744,7 +3114,7 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>47000</v>
       </c>
       <c r="H5" s="1">
@@ -2753,9 +3123,15 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>05/01/2000</v>
+      </c>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="str">
+        <v>05/06/2001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -2774,7 +3150,7 @@
       <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>50000</v>
       </c>
       <c r="H6" s="1">
@@ -2783,9 +3159,15 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>06/05/2001</v>
+      </c>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="str">
+        <v>12/07/1995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -2804,7 +3186,7 @@
       <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>65000</v>
       </c>
       <c r="H7" s="1">
@@ -2813,9 +3195,15 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>07/12/1995</v>
+      </c>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="str">
+        <v>11/08/2003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -2834,7 +3222,7 @@
       <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>41000</v>
       </c>
       <c r="H8" s="1">
@@ -2843,9 +3231,15 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>08/11/2003</v>
+      </c>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="str">
+        <v>06/09/2002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -2864,7 +3258,7 @@
       <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>48000</v>
       </c>
       <c r="H9" s="1">
@@ -2873,9 +3267,15 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>09/06/2002</v>
+      </c>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="str">
+        <v>08/10/2003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -2894,7 +3294,7 @@
       <c r="F10" t="s">
         <v>29</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>42000</v>
       </c>
       <c r="H10" s="1">
@@ -2903,12 +3303,18 @@
       <c r="I10" s="1">
         <v>40800</v>
       </c>
+      <c r="J10" t="str">
+        <v>10/08/2003</v>
+      </c>
       <c r="K10" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="str">
+        <v>00/01/1900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
     </row>
   </sheetData>
@@ -2921,14 +3327,24 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2962,8 +3378,11 @@
       <c r="K1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2980,7 +3399,7 @@
         <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G2">
         <v>45000</v>
@@ -2991,8 +3410,16 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TRIM(C2:C10)</f>
+        <v>Halpert</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">TRIM(PROPER(F2:F10))</f>
+        <v>Salesman</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -3020,8 +3447,14 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J3" t="str">
+        <v>Beasley</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Receptionist</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -3049,8 +3482,14 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J4" t="str">
+        <v>Schrute</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Salesman</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -3078,8 +3517,14 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" t="str">
+        <v>Martin</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Accountant</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -3107,8 +3552,14 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J6" t="str">
+        <v>Flenderson</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Hr</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -3125,7 +3576,7 @@
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="G7">
         <v>65000</v>
@@ -3136,8 +3587,14 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J7" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Regional Manager</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -3154,7 +3611,7 @@
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="G8">
         <v>41000</v>
@@ -3165,8 +3622,14 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J8" t="str">
+        <v>Palmer</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Supplier Relations</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -3194,8 +3657,14 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J9" t="str">
+        <v>Hudson</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Salesman</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -3222,6 +3691,12 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Accountant</v>
       </c>
     </row>
   </sheetData>
@@ -3230,6 +3705,388 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB977C31-5FD1-4473-A6A1-29ABAD3F7755}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>45000</v>
+      </c>
+      <c r="H2" s="1">
+        <v>37197</v>
+      </c>
+      <c r="I2" s="1">
+        <v>42253</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">CONCATENATE(B2:B10," ",C2:C10)</f>
+        <v>Jim Halpert</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">CONCATENATE(B2:B10,".",C2:C10,"@gmail.com")</f>
+        <v>Jim.Halpert@gmail.com</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <v>36000</v>
+      </c>
+      <c r="H3" s="1">
+        <v>36436</v>
+      </c>
+      <c r="I3" s="1">
+        <v>42287</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Pam Beasley</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pam.Beasley@gmail.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>63000</v>
+      </c>
+      <c r="H4" s="1">
+        <v>36711</v>
+      </c>
+      <c r="I4" s="1">
+        <v>42986</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Dwight Schrute</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Dwight.Schrute@gmail.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>47000</v>
+      </c>
+      <c r="H5" s="1">
+        <v>36530</v>
+      </c>
+      <c r="I5" s="1">
+        <v>42341</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Angela Martin</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Angela.Martin@gmail.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>50000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>37017</v>
+      </c>
+      <c r="I6" s="1">
+        <v>42977</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Toby Flenderson</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Toby.Flenderson@gmail.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>65000</v>
+      </c>
+      <c r="H7" s="1">
+        <v>35040</v>
+      </c>
+      <c r="I7" s="1">
+        <v>41528</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Michael Scott</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Michael.Scott@gmail.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>41000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>37933</v>
+      </c>
+      <c r="I8" s="1">
+        <v>41551</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Meredith Palmer</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Meredith.Palmer@gmail.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>48000</v>
+      </c>
+      <c r="H9" s="1">
+        <v>37416</v>
+      </c>
+      <c r="I9" s="1">
+        <v>42116</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Stanley Hudson</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Stanley.Hudson@gmail.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>42000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>37843</v>
+      </c>
+      <c r="I10" s="1">
+        <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Kevin Malone</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Kevin.Malone@gmail.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" t="str">
+        <f t="shared" ref="H11:H12" si="0">CONCATENATE(B11," ",C11)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0B9C42-087D-43BC-95CC-49AE54CDC17A}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -3307,6 +4164,18 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">SUBSTITUTE(H2:H10,"/","-",1)</f>
+        <v>11-2/2001</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">SUBSTITUTE(H2:H10,"/","-",2)</f>
+        <v>11/2-2001</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">SUBSTITUTE(H2:H10,"-","/")</f>
+        <v>11/2/2001</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -3336,6 +4205,15 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J3" t="str">
+        <v>10-3/1999</v>
+      </c>
+      <c r="K3" t="str">
+        <v>10/3-1999</v>
+      </c>
+      <c r="L3" t="str">
+        <v>10/3/1999</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -3365,6 +4243,15 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="J4" t="str">
+        <v>7-4/2000</v>
+      </c>
+      <c r="K4" t="str">
+        <v>7/4-2000</v>
+      </c>
+      <c r="L4" t="str">
+        <v>7/4/2000</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -3394,6 +4281,15 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J5" t="str">
+        <v>1-5/2000</v>
+      </c>
+      <c r="K5" t="str">
+        <v>1/5-2000</v>
+      </c>
+      <c r="L5" t="str">
+        <v>1/5/2000</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -3418,10 +4314,19 @@
         <v>50000</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="J6" t="str">
+        <v>5-6-2001</v>
+      </c>
+      <c r="K6" t="str">
+        <v>5-6/2001</v>
+      </c>
+      <c r="L6" t="str">
+        <v>5/6/2001</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -3452,6 +4357,15 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J7" t="str">
+        <v>5-6/2001</v>
+      </c>
+      <c r="K7" t="str">
+        <v>5/6-2001</v>
+      </c>
+      <c r="L7" t="str">
+        <v>5/6/2001</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -3481,6 +4395,15 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J8" t="str">
+        <v>11-8/2003</v>
+      </c>
+      <c r="K8" t="str">
+        <v>11/8-2003</v>
+      </c>
+      <c r="L8" t="str">
+        <v>11/8/2003</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -3510,6 +4433,15 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J9" t="str">
+        <v>6-9/2002</v>
+      </c>
+      <c r="K9" t="str">
+        <v>6/9-2002</v>
+      </c>
+      <c r="L9" t="str">
+        <v>6/9/2002</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -3538,6 +4470,15 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J10" t="str">
+        <v>8-10/2003</v>
+      </c>
+      <c r="K10" t="str">
+        <v>8/10-2003</v>
+      </c>
+      <c r="L10" t="str">
+        <v>8/10/2003</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +4523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D41C5D0-EC67-4288-8B29-30C6E5CFEE73}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -3656,321 +4597,17 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3">
-        <v>36000</v>
-      </c>
-      <c r="H3" s="1">
-        <v>36436</v>
-      </c>
-      <c r="I3" s="1">
-        <v>42287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4">
-        <v>63000</v>
-      </c>
-      <c r="H4" s="1">
-        <v>36711</v>
-      </c>
-      <c r="I4" s="1">
-        <v>42986</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>47000</v>
-      </c>
-      <c r="H5" s="1">
-        <v>36530</v>
-      </c>
-      <c r="I5" s="1">
-        <v>42341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="1">
-        <v>37017</v>
-      </c>
-      <c r="I6" s="1">
-        <v>42977</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7">
-        <v>65000</v>
-      </c>
-      <c r="H7" s="1">
-        <v>35040</v>
-      </c>
-      <c r="I7" s="1">
-        <v>41528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8">
-        <v>41000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>37933</v>
-      </c>
-      <c r="I8" s="1">
-        <v>41551</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9">
-        <v>48000</v>
-      </c>
-      <c r="H9" s="1">
-        <v>37416</v>
-      </c>
-      <c r="I9" s="1">
-        <v>42116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10">
-        <v>42000</v>
-      </c>
-      <c r="H10" s="1">
-        <v>37843</v>
-      </c>
-      <c r="I10" s="1">
-        <v>40800</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D217F6E-9452-40AF-AFA2-377600A25F44}">
-  <sheetPr>
-    <tabColor theme="9"/>
-  </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2">
-        <v>45000</v>
-      </c>
-      <c r="H2" s="1">
-        <v>37197</v>
-      </c>
-      <c r="I2" s="1">
-        <v>42253</v>
+      <c r="J2">
+        <f>SUM(G2:G10)</f>
+        <v>437000</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(G2:G10,"&gt;50000")</f>
+        <v>128000</v>
+      </c>
+      <c r="L2">
+        <f>SUMIFS(G2:G10,E2:E10,"Female",D2:D10,"&gt;30")</f>
+        <v>88000</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
